--- a/기능명세서.xlsx
+++ b/기능명세서.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1331,55 +1331,56 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6-3. DB 기반 조건 평가</t>
+          <t>6-3. 조건 설명 제공</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>6-3-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
-6-3-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
+          <t>6-3-1-1. 각 조건 칩의 ⓘ 버튼으로 쉬운 말 설명 팝오버를 표시한다.
+6-3-1-2. 설명 텍스트는 조건 정의에 정적으로 포함된다.</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>일봉 OHLCV, 투자자 데이터</t>
+          <t>조건 설명 텍스트</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ScreenerResult</t>
+          <t>ConditionItem</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>스크리너 결과 목록</t>
+          <t>조건 설명 팝오버</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>services.screener_conditions</t>
+          <t>web</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6-4. 실시간 조건 평가</t>
+          <t>6-4. DB 기반 조건 평가</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>6-4-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
+          <t>6-4-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
+6-4-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>체결강도, 신고가, 상한가</t>
+          <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>RankItem</t>
+          <t>ScreenerResult</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1389,96 +1390,96 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>services.ranking</t>
+          <t>services.screener_conditions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6-5. 야간 데이터 수집 배치</t>
+          <t>6-5. 실시간 조건 평가</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>6-5-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
+          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>체결강도, 신고가, 상한가</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>스크리너 결과 목록</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>6-6. 야간 데이터 수집 배치</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>6-6-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>ScreenerDB</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>services.screener_collector</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>7. 시장현황 랭킹</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>7-1. 거래량/거래대금 순위</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>거래량, 거래대금 순위</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>시장현황 랭킹 화면</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
-        </is>
-      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>7-2. 급등주 순위</t>
+          <t>7-1. 거래량/거래대금 순위</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
+          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>등락률 순위</t>
+          <t>거래량, 거래대금 순위</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1500,17 +1501,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>7-3. 외국인/기관 순매수 순위</t>
+          <t>7-2. 급등주 순위</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>순매수량 순위</t>
+          <t>등락률 순위</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1532,226 +1533,230 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>7-3. 외국인/기관 순매수 순위</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>순매수량 순위</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>시장현황 랭킹 화면</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>7-4. 자동 갱신</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>7-4-1-1. 실시간 탭은 15초마다 데이터를 갱신한다.</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>순위 목록</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>RankItem</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>시장현황 랭킹 화면</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>8. 종목 탐색 · 화면 흐름</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>8-1. 종목 검색</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>종목명, 종목코드</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>StockMaster</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>헤더 검색창</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>services.outlook</t>
-        </is>
-      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8-2. 호버 미리보기</t>
+          <t>8-1. 종목 검색</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>미니 차트, 한줄요약, 시세</t>
+          <t>종목명, 종목코드</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>MarketQuote</t>
+          <t>StockMaster</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>우측 미리보기 패널</t>
+          <t>헤더 검색창</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.outlook</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>8-2. 호버 미리보기</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>미니 차트, 한줄요약, 시세</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>MarketQuote</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>우측 미리보기 패널</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>8-3. URL 라우팅 · 뒤로가기 복원</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>8-3-1-1. 종목 진입 시 URL에 종목코드를 반영한다.
 8-3-1-2. 뒤로가기 시 직전 탭·스크롤 위치·스크리너 조건을 복원한다.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>종목코드, 화면 상태</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>HistoryState</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>8-4. 종목 로고 표시</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>8-4-1-1. 종목별 로고 이미지를 CDN에서 불러와 표시한다.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>로고 이미지</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>StockLogo</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>종목 목록·상세</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>9. 공통 · 환경</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>9-1. 뉴스 수집</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>뉴스 기사</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>9-2. 공시 수집</t>
+          <t>9-1. 뉴스 수집</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
+          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>공시 항목</t>
+          <t>뉴스 기사</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1762,65 +1767,93 @@
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>disclosure</t>
+          <t>news</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>9-3. 큰 글씨 모드</t>
+          <t>9-2. 공시 수집</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>확대 배율</t>
+          <t>공시 항목</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ThemeState</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>큰 글씨 토글</t>
-        </is>
-      </c>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>disclosure</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>9-3. 큰 글씨 모드</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>확대 배율</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>ThemeState</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>큰 글씨 토글</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>9-4. KIS 인증</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>9-4-1-1. KIS Open API 접근 토큰과 WebSocket approval_key를 발급·관리한다.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>접근 토큰, approval_key</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>KISAuth</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>services</t>
         </is>

--- a/기능명세서.xlsx
+++ b/기능명세서.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1253,73 +1253,76 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>5-5. 차트 패턴 유사 사례 검색</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>5-5-1-1. 고른 구간 종가를 z-정규화한다.
+5-5-1-2. 전 종목 슬라이딩 윈도우를 유클리드 거리로 1차 필터링한다.
+5-5-1-3. 상위 후보를 DTW(Sakoe-Chiba 밴드)로 재정렬한다.
+5-5-1-4. 각 사례의 이후 N일 수익률을 집계해 통계(평균·중앙값·상승비율)를 낸다.</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>종가 시계열, 유사도, 이후 수익률</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SimilarCase</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>유사 패턴 검색 카드</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>chart.pattern_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>6. 다중 조건 검색식</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>6-1. 조건 선택</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>6-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>조건 목록</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>ScreenerCondition</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>스크리너 조건 선택 화면</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6-2. 조건 파라미터 설정</t>
+          <t>6-1. 조건 선택</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>6-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
+          <t>6-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>임계값, 일수, 기간</t>
+          <t>조건 목록</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ScreenerParams</t>
+          <t>ScreenerCondition</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>조건 파라미터 팝오버</t>
+          <t>스크리너 조건 선택 화면</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1331,187 +1334,187 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>6-2. 조건 파라미터 설정</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>6-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>임계값, 일수, 기간</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>ScreenerParams</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>조건 파라미터 팝오버</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>6-3. 조건 설명 제공</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>6-3-1-1. 각 조건 칩의 ⓘ 버튼으로 쉬운 말 설명 팝오버를 표시한다.
 6-3-1-2. 설명 텍스트는 조건 정의에 정적으로 포함된다.</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>조건 설명 텍스트</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>ConditionItem</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>조건 설명 팝오버</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>6-4. DB 기반 조건 평가</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>6-4-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
 6-4-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>ScreenerResult</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>스크리너 결과 목록</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>services.screener_conditions</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>6-5. 실시간 조건 평가</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>체결강도, 신고가, 상한가</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>스크리너 결과 목록</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>6-5. 실시간 조건 평가</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>체결강도, 신고가, 상한가</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>스크리너 결과 목록</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>6-6. 야간 데이터 수집 배치</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>6-6-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>ScreenerDB</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>services.screener_collector</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>7. 시장현황 랭킹</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>7-1. 거래량/거래대금 순위</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>거래량, 거래대금 순위</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>시장현황 랭킹 화면</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
-        </is>
-      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>7-2. 급등주 순위</t>
+          <t>7-1. 거래량/거래대금 순위</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
+          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>등락률 순위</t>
+          <t>거래량, 거래대금 순위</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1533,17 +1536,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7-3. 외국인/기관 순매수 순위</t>
+          <t>7-2. 급등주 순위</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>순매수량 순위</t>
+          <t>등락률 순위</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1565,226 +1568,230 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>7-3. 외국인/기관 순매수 순위</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>순매수량 순위</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>시장현황 랭킹 화면</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>7-4. 자동 갱신</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>7-4-1-1. 실시간 탭은 15초마다 데이터를 갱신한다.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>순위 목록</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>RankItem</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>시장현황 랭킹 화면</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>8. 종목 탐색 · 화면 흐름</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>8-1. 종목 검색</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>종목명, 종목코드</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>StockMaster</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>헤더 검색창</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>services.outlook</t>
-        </is>
-      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8-2. 호버 미리보기</t>
+          <t>8-1. 종목 검색</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>미니 차트, 한줄요약, 시세</t>
+          <t>종목명, 종목코드</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>MarketQuote</t>
+          <t>StockMaster</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>우측 미리보기 패널</t>
+          <t>헤더 검색창</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.outlook</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>8-2. 호버 미리보기</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>미니 차트, 한줄요약, 시세</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>MarketQuote</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>우측 미리보기 패널</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
           <t>8-3. URL 라우팅 · 뒤로가기 복원</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>8-3-1-1. 종목 진입 시 URL에 종목코드를 반영한다.
 8-3-1-2. 뒤로가기 시 직전 탭·스크롤 위치·스크리너 조건을 복원한다.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>종목코드, 화면 상태</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>HistoryState</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>8-4. 종목 로고 표시</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>8-4-1-1. 종목별 로고 이미지를 CDN에서 불러와 표시한다.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>로고 이미지</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>StockLogo</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>종목 목록·상세</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>9. 공통 · 환경</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>9-1. 뉴스 수집</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>뉴스 기사</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>9-2. 공시 수집</t>
+          <t>9-1. 뉴스 수집</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
+          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>공시 항목</t>
+          <t>뉴스 기사</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -1795,65 +1802,93 @@
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>disclosure</t>
+          <t>news</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9-3. 큰 글씨 모드</t>
+          <t>9-2. 공시 수집</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>확대 배율</t>
+          <t>공시 항목</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ThemeState</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>큰 글씨 토글</t>
-        </is>
-      </c>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>disclosure</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>9-3. 큰 글씨 모드</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>확대 배율</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>ThemeState</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>큰 글씨 토글</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>9-4. KIS 인증</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>9-4-1-1. KIS Open API 접근 토큰과 WebSocket approval_key를 발급·관리한다.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>접근 토큰, approval_key</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>KISAuth</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>services</t>
         </is>

--- a/기능명세서.xlsx
+++ b/기능명세서.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1261,14 +1261,15 @@
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>5-5-1-1. 고른 구간 종가를 z-정규화한다.
-5-5-1-2. 전 종목 슬라이딩 윈도우를 유클리드 거리로 1차 필터링한다.
-5-5-1-3. 상위 후보를 DTW(Sakoe-Chiba 밴드)로 재정렬한다.
-5-5-1-4. 각 사례의 이후 N일 수익률을 집계해 통계(평균·중앙값·상승비율)를 낸다.</t>
+5-5-1-2. 전 종목(약 2,700) 슬라이딩 윈도우를 유클리드 거리로 1차 필터링한다.
+5-5-1-3. 선택 지표(DTW/피어슨/스피어만)로 정밀 점수·정렬한다.
+5-5-1-4. 결과 개수·최소 유사도(컷오프)를 적용한다.
+5-5-1-5. 각 사례의 이후 N일 수익률을 집계해 통계(평균·중앙값·상승비율)를 낸다.</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>종가 시계열, 유사도, 이후 수익률</t>
+          <t>종가 시계열, 유사도 지표, 컷오프, 이후 수익률</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1288,73 +1289,75 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>5-6. 유사 사례 실제 차트 비교</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>5-6-1-1. 사례 선택 시 해당 종목 일봉을 조회해 유사 구간+이후 캔들을 그린다.
+5-6-1-2. 현재 종목 구간과 좌우로 나란히 비교 표시한다.
+5-6-1-3. 매칭 끝 시점에 '현재 시점' 세로선을 표시해 이후 흐름을 구분한다.</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>일봉 OHLCV, 매칭 종료 시점</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>OHLCVBar</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>유사 패턴 비교 차트</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>6. 다중 조건 검색식</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>6-1. 조건 선택</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>6-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>조건 목록</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>ScreenerCondition</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>스크리너 조건 선택 화면</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6-2. 조건 파라미터 설정</t>
+          <t>6-1. 조건 선택</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>6-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
+          <t>6-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>임계값, 일수, 기간</t>
+          <t>조건 목록</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ScreenerParams</t>
+          <t>ScreenerCondition</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>조건 파라미터 팝오버</t>
+          <t>스크리너 조건 선택 화면</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1366,187 +1369,187 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>6-2. 조건 파라미터 설정</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>6-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>임계값, 일수, 기간</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ScreenerParams</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>조건 파라미터 팝오버</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>6-3. 조건 설명 제공</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>6-3-1-1. 각 조건 칩의 ⓘ 버튼으로 쉬운 말 설명 팝오버를 표시한다.
 6-3-1-2. 설명 텍스트는 조건 정의에 정적으로 포함된다.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>조건 설명 텍스트</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>ConditionItem</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>조건 설명 팝오버</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>6-4. DB 기반 조건 평가</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>6-4-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
 6-4-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>ScreenerResult</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>스크리너 결과 목록</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>services.screener_conditions</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>6-5. 실시간 조건 평가</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>체결강도, 신고가, 상한가</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>스크리너 결과 목록</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>6-5. 실시간 조건 평가</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>체결강도, 신고가, 상한가</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>스크리너 결과 목록</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
           <t>6-6. 야간 데이터 수집 배치</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>6-6-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>ScreenerDB</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>services.screener_collector</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>7. 시장현황 랭킹</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>7-1. 거래량/거래대금 순위</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>거래량, 거래대금 순위</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>시장현황 랭킹 화면</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
-        </is>
-      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7-2. 급등주 순위</t>
+          <t>7-1. 거래량/거래대금 순위</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
+          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>등락률 순위</t>
+          <t>거래량, 거래대금 순위</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1568,17 +1571,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>7-3. 외국인/기관 순매수 순위</t>
+          <t>7-2. 급등주 순위</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>순매수량 순위</t>
+          <t>등락률 순위</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1600,226 +1603,230 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>7-3. 외국인/기관 순매수 순위</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>순매수량 순위</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>시장현황 랭킹 화면</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>7-4. 자동 갱신</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>7-4-1-1. 실시간 탭은 15초마다 데이터를 갱신한다.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>순위 목록</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>RankItem</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>시장현황 랭킹 화면</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>8. 종목 탐색 · 화면 흐름</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>8-1. 종목 검색</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>종목명, 종목코드</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>StockMaster</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>헤더 검색창</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>services.outlook</t>
-        </is>
-      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8-2. 호버 미리보기</t>
+          <t>8-1. 종목 검색</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>미니 차트, 한줄요약, 시세</t>
+          <t>종목명, 종목코드</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>MarketQuote</t>
+          <t>StockMaster</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>우측 미리보기 패널</t>
+          <t>헤더 검색창</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.outlook</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>8-2. 호버 미리보기</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>미니 차트, 한줄요약, 시세</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>MarketQuote</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>우측 미리보기 패널</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>8-3. URL 라우팅 · 뒤로가기 복원</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>8-3-1-1. 종목 진입 시 URL에 종목코드를 반영한다.
 8-3-1-2. 뒤로가기 시 직전 탭·스크롤 위치·스크리너 조건을 복원한다.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>종목코드, 화면 상태</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>HistoryState</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>8-4. 종목 로고 표시</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>8-4-1-1. 종목별 로고 이미지를 CDN에서 불러와 표시한다.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>로고 이미지</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>StockLogo</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>종목 목록·상세</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>9. 공통 · 환경</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>9-1. 뉴스 수집</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>뉴스 기사</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9-2. 공시 수집</t>
+          <t>9-1. 뉴스 수집</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
+          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>공시 항목</t>
+          <t>뉴스 기사</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -1830,65 +1837,93 @@
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>disclosure</t>
+          <t>news</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9-3. 큰 글씨 모드</t>
+          <t>9-2. 공시 수집</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>확대 배율</t>
+          <t>공시 항목</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ThemeState</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>큰 글씨 토글</t>
-        </is>
-      </c>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>disclosure</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>9-3. 큰 글씨 모드</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>확대 배율</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>ThemeState</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>큰 글씨 토글</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
           <t>9-4. KIS 인증</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>9-4-1-1. KIS Open API 접근 토큰과 WebSocket approval_key를 발급·관리한다.</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>접근 토큰, approval_key</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>KISAuth</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>services</t>
         </is>

--- a/기능명세서.xlsx
+++ b/기능명세서.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1325,7 +1325,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>6. 다중 조건 검색식</t>
+          <t>6. 업종별 추천</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -1337,219 +1337,225 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6-1. 조건 선택</t>
+          <t>6-1. 업종 목록 조회</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>6-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
+          <t>6-1-1-1. kospi_category.csv·kosdaq_category.csv에서 업종명을 stocks.sector 컬럼에 저장한다.
+6-1-1-2. daily_price 데이터가 있는 종목 기준으로 업종명·종목수를 집계해 반환한다.</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>조건 목록</t>
+          <t>업종명, 종목수</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ScreenerCondition</t>
+          <t>SectorInfo</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>스크리너 조건 선택 화면</t>
+          <t>업종 추천 화면</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.sector, services.screener_db</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6-2. 조건 파라미터 설정</t>
+          <t>6-2. 업종 내 top 3 추천</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>6-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
+          <t>6-2-1-1. 업종 내 종목을 모멘텀 스코어(20일 가격 모멘텀 × 0.6 + 거래량 서지 × 0.4)로 정렬한다.
+6-2-1-2. 상위 3종목의 종목코드·이름·현재가·등락률을 반환한다.</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>임계값, 일수, 기간</t>
+          <t>종가 시계열, 거래량</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>ScreenerParams</t>
+          <t>SectorPick</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>조건 파라미터 팝오버</t>
+          <t>업종 추천 결과 목록</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.sector</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>6-3. 조건 설명 제공</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>6-3-1-1. 각 조건 칩의 ⓘ 버튼으로 쉬운 말 설명 팝오버를 표시한다.
-6-3-1-2. 설명 텍스트는 조건 정의에 정적으로 포함된다.</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>조건 설명 텍스트</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>ConditionItem</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>조건 설명 팝오버</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>7. 다중 조건 검색식</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6-4. DB 기반 조건 평가</t>
+          <t>7-1. 조건 선택</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>6-4-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
-6-4-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
+          <t>7-1-1-1. 28종 조건을 카테고리별 칩으로 다중 선택한다.</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>일봉 OHLCV, 투자자 데이터</t>
+          <t>조건 목록</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>ScreenerResult</t>
+          <t>ScreenerCondition</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>스크리너 결과 목록</t>
+          <t>스크리너 조건 선택 화면</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>services.screener_conditions</t>
+          <t>web</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6-5. 실시간 조건 평가</t>
+          <t>7-2. 조건 파라미터 설정</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>6-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
+          <t>7-2-1-1. 조건별 임계값(배수·일수·기간 등)을 칩 팝오버로 조정한다.</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>체결강도, 신고가, 상한가</t>
+          <t>임계값, 일수, 기간</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>RankItem</t>
+          <t>ScreenerParams</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>스크리너 결과 목록</t>
+          <t>조건 파라미터 팝오버</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>services.ranking</t>
+          <t>web</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6-6. 야간 데이터 수집 배치</t>
+          <t>7-3. 조건 설명 제공</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>6-6-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
+          <t>7-3-1-1. 각 조건 칩의 ⓘ 버튼으로 쉬운 말 설명 팝오버를 표시한다.
+7-3-1-2. 설명 텍스트는 조건 정의에 정적으로 포함된다.</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
+          <t>조건 설명 텍스트</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>ConditionItem</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>조건 설명 팝오버</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>7-4. DB 기반 조건 평가</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>7-4-1-1. 사전 수집된 일봉·투자자 데이터로 전체 종목을 검사한다.
+7-4-1-2. 거래량 급등·골든크로스·정배열·MACD·OBV 등 25종 조건을 계산한다.</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
           <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>ScreenerDB</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>services.screener_collector</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>7. 시장현황 랭킹</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>ScreenerResult</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>스크리너 결과 목록</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>services.screener_conditions</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7-1. 거래량/거래대금 순위</t>
+          <t>7-5. 실시간 조건 평가</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>7-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
+          <t>7-5-1-1. 체결강도·신고가 근접·상한가 포착 3종은 KIS API로 실시간 조회한다.</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>거래량, 거래대금 순위</t>
+          <t>체결강도, 신고가, 상한가</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1559,7 +1565,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>시장현황 랭킹 화면</t>
+          <t>스크리너 결과 목록</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1571,81 +1577,57 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>7-2. 급등주 순위</t>
+          <t>7-6. 야간 데이터 수집 배치</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>7-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
+          <t>7-6-1-1. 전 종목 일봉 OHLCV와 투자자 데이터를 매일 수집해 SQLite에 저장한다.</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>등락률 순위</t>
+          <t>일봉 OHLCV, 투자자 데이터</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>시장현황 랭킹 화면</t>
-        </is>
-      </c>
+          <t>ScreenerDB</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>services.ranking</t>
+          <t>services.screener_collector</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>7-3. 외국인/기관 순매수 순위</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>7-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>순매수량 순위</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>RankItem</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>시장현황 랭킹 화면</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>services.ranking</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>8. 시장현황 랭킹</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7-4. 자동 갱신</t>
+          <t>8-1. 거래량/거래대금 순위</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>7-4-1-1. 실시간 탭은 15초마다 데이터를 갱신한다.</t>
+          <t>8-1-1-1. 거래량·거래대금 상위 종목을 조회한다.</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>순위 목록</t>
+          <t>거래량, 거래대금 순위</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1660,78 +1642,98 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>services.ranking</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>8. 종목 탐색 · 화면 흐름</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>8-2. 급등주 순위</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>8-2-1-1. 등락률 상위 종목을 양수 등락률만 필터링해 조회한다.</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>등락률 순위</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>RankItem</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>시장현황 랭킹 화면</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>services.ranking</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8-1. 종목 검색</t>
+          <t>8-3. 외국인/기관 순매수 순위</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>8-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
+          <t>8-3-1-1. 외국인·기관 순매수 상위 종목을 조회한다.</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>종목명, 종목코드</t>
+          <t>순매수량 순위</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>StockMaster</t>
+          <t>RankItem</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>헤더 검색창</t>
+          <t>시장현황 랭킹 화면</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>services.outlook</t>
+          <t>services.ranking</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8-2. 호버 미리보기</t>
+          <t>8-4. 자동 갱신</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>8-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+          <t>8-4-1-1. 실시간 탭은 15초마다 데이터를 갱신한다.</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>미니 차트, 한줄요약, 시세</t>
+          <t>순위 목록</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>MarketQuote</t>
+          <t>RankItem</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>우측 미리보기 패널</t>
+          <t>시장현황 랭킹 화면</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -1741,189 +1743,265 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>8-3. URL 라우팅 · 뒤로가기 복원</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>8-3-1-1. 종목 진입 시 URL에 종목코드를 반영한다.
-8-3-1-2. 뒤로가기 시 직전 탭·스크롤 위치·스크리너 조건을 복원한다.</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>종목코드, 화면 상태</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>HistoryState</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9. 종목 탐색 · 화면 흐름</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8-4. 종목 로고 표시</t>
+          <t>9-1. 종목 검색</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>8-4-1-1. 종목별 로고 이미지를 CDN에서 불러와 표시한다.</t>
+          <t>9-1-1-1. 종목명·코드로 검색해 상세 페이지로 이동한다.</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>로고 이미지</t>
+          <t>종목명, 종목코드</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>StockLogo</t>
+          <t>StockMaster</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>종목 목록·상세</t>
+          <t>헤더 검색창</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
+          <t>services.outlook</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>9-2. 호버 미리보기</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>9-2-1-1. 목록에서 종목 호버 시 미니 차트·한줄요약·시세를 우측 패널에 표시한다.</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>미니 차트, 한줄요약, 시세</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>MarketQuote</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>우측 미리보기 패널</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
           <t>web</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>9. 공통 · 환경</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9-1. 뉴스 수집</t>
+          <t>9-3. URL 라우팅 · 뒤로가기 복원</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>9-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
+          <t>9-3-1-1. 종목 진입 시 URL에 종목코드를 반영한다.
+9-3-1-2. 뒤로가기 시 직전 탭·스크롤 위치·스크리너 조건을 복원한다.</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>뉴스 기사</t>
+          <t>종목코드, 화면 상태</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>HistoryState</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>web</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9-2. 공시 수집</t>
+          <t>9-4. 종목 로고 표시</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>9-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
+          <t>9-4-1-1. 종목별 로고 이미지를 CDN에서 불러와 표시한다.</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>공시 항목</t>
+          <t>로고 이미지</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
+          <t>StockLogo</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>종목 목록·상세</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>disclosure</t>
+          <t>web</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>9-3. 큰 글씨 모드</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>9-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>확대 배율</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>ThemeState</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>큰 글씨 토글</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>10. 공통 · 환경</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9-4. KIS 인증</t>
+          <t>10-1. 뉴스 수집</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>9-4-1-1. KIS Open API 접근 토큰과 WebSocket approval_key를 발급·관리한다.</t>
+          <t>10-1-1-1. 종목 관련 뉴스를 수집해 evidence로 만든다.</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>접근 토큰, approval_key</t>
+          <t>뉴스 기사</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>KISAuth</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>10-2. 공시 수집</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>10-2-1-1. DART 등에서 공시를 수집해 evidence로 만든다.</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>공시 항목</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>10-3. 큰 글씨 모드</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>10-3-1-1. 토글로 전체 화면을 1.3배 확대한다.</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>확대 배율</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>ThemeState</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>큰 글씨 토글</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>10-4. KIS 인증</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>10-4-1-1. KIS Open API 접근 토큰과 WebSocket approval_key를 발급·관리한다.</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>접근 토큰, approval_key</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>KISAuth</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>services</t>
         </is>
